--- a/プロンプト　テンプレート.xlsm.xlsx
+++ b/プロンプト　テンプレート.xlsm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vscode作成\Practice-problem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A472F8BE-10FA-4A4D-B813-063E4E191318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA6DC17-65A1-4365-B391-CF4457A84587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22450" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CE692CE3-F010-416D-A943-D49DC02ADD8E}"/>
   </bookViews>
@@ -78,18 +78,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>微生物</t>
-    <rPh sb="0" eb="3">
-      <t>ビセイブツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>one</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>five</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -117,6 +106,20 @@
     <rPh sb="10" eb="11">
       <t>カタ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小児_事後課題</t>
+    <rPh sb="0" eb="2">
+      <t>ショウニ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ジゴカダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>seventy</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -124,7 +127,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,6 +150,13 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="4">
@@ -264,7 +274,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="36576" rIns="27432" bIns="36576" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="54864" rIns="36576" bIns="54864" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -598,7 +608,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" ht="35" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -608,11 +618,11 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="str">
         <f>A3 &amp; "フォルダ内にあるhtmlファイルを以下のように修正してほしい。"</f>
-        <v>微生物フォルダ内にあるhtmlファイルを以下のように修正してほしい。</v>
+        <v>小児_事後課題フォルダ内にあるhtmlファイルを以下のように修正してほしい。</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -622,16 +632,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" t="str">
         <f>"・" &amp; A6 &amp; "フォルダ内の「one.html」が理想の形のため、" &amp; A6 &amp; "フォルダ内の「one.html」を参考に、「" &amp; A3 &amp; " 」フォルダ内の「 " &amp; A9 &amp; ".html」から「 " &amp; B9 &amp; ".html」を修正してください。"</f>
-        <v>・疾病1_1回目フォルダ内の「one.html」が理想の形のため、疾病1_1回目フォルダ内の「one.html」を参考に、「微生物 」フォルダ内の「 one.html」から「 five.html」を修正してください。</v>
+        <v>・疾病1_1回目フォルダ内の「one.html」が理想の形のため、疾病1_1回目フォルダ内の「one.html」を参考に、「小児_事後課題 」フォルダ内の「 one.html」から「 seventy.html」を修正してください。</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -644,14 +654,14 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9" t="str">
         <f>"１，「" &amp; A9 &amp; ".html」から「" &amp; B9 &amp; ".html」までのすべてのファイルを、" &amp; A3 &amp; "「one.html」の形式に統一したいということです。"</f>
-        <v>１，「one.html」から「five.html」までのすべてのファイルを、微生物「one.html」の形式に統一したいということです。</v>
+        <v>１，「one.html」から「seventy.html」までのすべてのファイルを、小児_事後課題「one.html」の形式に統一したいということです。</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -672,7 +682,7 @@
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D16" t="str">
         <f>"・" &amp; A3 &amp; "フォルダ内「one.html」の【選択肢の解説】内で記載しているように、「選択肢番号、選択肢、→選択肢が正・誤の理由を一文で簡潔に」整えてください。"</f>
-        <v>・微生物フォルダ内「one.html」の【選択肢の解説】内で記載しているように、「選択肢番号、選択肢、→選択肢が正・誤の理由を一文で簡潔に」整えてください。</v>
+        <v>・小児_事後課題フォルダ内「one.html」の【選択肢の解説】内で記載しているように、「選択肢番号、選択肢、→選択肢が正・誤の理由を一文で簡潔に」整えてください。</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -682,11 +692,11 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="D18" t="str">
         <f>"３，修正対象のフォルダは、「" &amp; A3 &amp; "」です。修正対象のhtmlは、「" &amp; A9 &amp; ".html」から「" &amp; B9 &amp; ".html」の" &amp; A18 &amp; "htmlファイルです。"</f>
-        <v>３，修正対象のフォルダは、「微生物」です。修正対象のhtmlは、「one.html」から「five.html」の5htmlファイルです。</v>
+        <v>３，修正対象のフォルダは、「小児_事後課題」です。修正対象のhtmlは、「one.html」から「seventy.html」の70htmlファイルです。</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -697,7 +707,7 @@
     <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D21" t="str">
         <f>"１，現在の" &amp; A9 &amp; ".html～" &amp; B9 &amp; " .htmlのファイル内に、one.htmlのような詳細な説明文は記載されていません。説明文を考えて追加していただきたいのですが可能でしょうか。可能であれば、簡潔に一文で説明文を追加していただきたいです。"</f>
-        <v>１，現在のone.html～five .htmlのファイル内に、one.htmlのような詳細な説明文は記載されていません。説明文を考えて追加していただきたいのですが可能でしょうか。可能であれば、簡潔に一文で説明文を追加していただきたいです。</v>
+        <v>１，現在のone.html～seventy .htmlのファイル内に、one.htmlのような詳細な説明文は記載されていません。説明文を考えて追加していただきたいのですが可能でしょうか。可能であれば、簡潔に一文で説明文を追加していただきたいです。</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">

--- a/プロンプト　テンプレート.xlsm.xlsx
+++ b/プロンプト　テンプレート.xlsm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vscode作成\Practice-problem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA6DC17-65A1-4365-B391-CF4457A84587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540E4B50-AB9C-4CFE-9563-D6FEACEA39F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22450" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CE692CE3-F010-416D-A943-D49DC02ADD8E}"/>
   </bookViews>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>　※実行する前に分からないことは質問してください。</t>
   </si>
   <si>
-    <t>【追加１】</t>
-  </si>
-  <si>
     <t>２，特に修正してほしい項目は以下です。</t>
   </si>
   <si>
@@ -40,9 +37,6 @@
   </si>
   <si>
     <t>・【選択肢の解説】内に記載されている&lt;li&gt;タグをone.htmlと同じように改行してください。</t>
-  </si>
-  <si>
-    <t>【追加２】</t>
   </si>
   <si>
     <t>※各ファイルの詳細な説明文は有りで進めていただきたいです。</t>
@@ -109,17 +103,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>小児_事後課題</t>
+    <t>母性</t>
     <rPh sb="0" eb="2">
-      <t>ショウニ</t>
-    </rPh>
-    <rPh sb="3" eb="7">
-      <t>ジゴカダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>seventy</t>
+      <t>ボセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※「疾病1_1回目」フォルダ内はファイル名も含めてすべてが理想形です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>twentythree</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -233,16 +228,16 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor>
         <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>12700</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>383931</xdr:colOff>
           <xdr:row>22</xdr:row>
-          <xdr:rowOff>222250</xdr:rowOff>
+          <xdr:rowOff>56173</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>572967</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>64966</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -599,7 +594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2D17BC-68C3-4D27-866E-E9E249502B26}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
@@ -608,21 +603,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" ht="35" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3" t="str">
-        <f>A3 &amp; "フォルダ内にあるhtmlファイルを以下のように修正してほしい。"</f>
-        <v>小児_事後課題フォルダ内にあるhtmlファイルを以下のように修正してほしい。</v>
+        <f>A3 &amp; "フォルダ内にあるhtmlファイルを以下のように修正してください。" &amp; A6 &amp; "フォルダ内に無い機能や説明文などは追加しないでください。"</f>
+        <v>母性フォルダ内にあるhtmlファイルを以下のように修正してください。疾病1_1回目フォルダ内に無い機能や説明文などは追加しないでください。</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -632,87 +627,96 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" t="str">
-        <f>"・" &amp; A6 &amp; "フォルダ内の「one.html」が理想の形のため、" &amp; A6 &amp; "フォルダ内の「one.html」を参考に、「" &amp; A3 &amp; " 」フォルダ内の「 " &amp; A9 &amp; ".html」から「 " &amp; B9 &amp; ".html」を修正してください。"</f>
-        <v>・疾病1_1回目フォルダ内の「one.html」が理想の形のため、疾病1_1回目フォルダ内の「one.html」を参考に、「小児_事後課題 」フォルダ内の「 one.html」から「 seventy.html」を修正してください。</v>
+        <f>"・" &amp; A6 &amp; "フォルダ内の「one.html」が理想の形のため、" &amp; A6 &amp; "フォルダ内の「one.html」を参考に、「" &amp; A3 &amp; " 」フォルダ内の「 " &amp; A12 &amp; ".html」から「 " &amp; B12 &amp; ".html」を修正してください。"</f>
+        <v>・疾病1_1回目フォルダ内の「one.html」が理想の形のため、疾病1_1回目フォルダ内の「one.html」を参考に、「母性 」フォルダ内の「 one.html」から「 twentythree.html」を修正してください。</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="D7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
+      <c r="D8" t="str">
+        <f>"・htmlファイルがない場合は、理想の形としている「" &amp; A6 &amp; "フォルダ内」のようにhtmlファイルを新規で作成してください。※ファイル名も理想の形である「" &amp; A6 &amp; "」と同様に修正してください。"</f>
+        <v>・htmlファイルがない場合は、理想の形としている「疾病1_1回目フォルダ内」のようにhtmlファイルを新規で作成してください。※ファイル名も理想の形である「疾病1_1回目」と同様に修正してください。</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="D9" t="str">
+        <f>"・「javascript」「CSS」ファイルが" &amp; A3 &amp; "フォルダ内にない場合、「" &amp; A6 &amp; "フォルダ内から、「javascript」「CSS」ファイルをコピペして追加してください。"</f>
+        <v>・「javascript」「CSS」ファイルが母性フォルダ内にない場合、「疾病1_1回目フォルダ内から、「javascript」「CSS」ファイルをコピペして追加してください。</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="str">
+        <f>"１，「" &amp; A12 &amp; ".html」から「" &amp; B12 &amp; ".html」までのすべてのファイルを、" &amp; A3 &amp; "「one.html」の形式に統一したいということです。"</f>
+        <v>１，「one.html」から「twentythree.html」までのすべてのファイルを、母性「one.html」の形式に統一したいということです。</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D8" t="s">
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="D13" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="str">
-        <f>"１，「" &amp; A9 &amp; ".html」から「" &amp; B9 &amp; ".html」までのすべてのファイルを、" &amp; A3 &amp; "「one.html」の形式に統一したいということです。"</f>
-        <v>１，「one.html」から「seventy.html」までのすべてのファイルを、小児_事後課題「one.html」の形式に統一したいということです。</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="D11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="D12" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="D16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="D18" t="str">
+        <f>"・" &amp; A3 &amp; "フォルダ内「one.html」の【選択肢の解説】内で記載しているように、「選択肢番号、選択肢、→選択肢が正・誤の理由を一文で簡潔に」整えてください。"</f>
+        <v>・母性フォルダ内「one.html」の【選択肢の解説】内で記載しているように、「選択肢番号、選択肢、→選択肢が正・誤の理由を一文で簡潔に」整えてください。</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="str">
+        <f>"３，修正対象のフォルダは、「" &amp; A3 &amp; "」です。修正対象のhtmlは、「" &amp; A12 &amp; ".html」から「" &amp; B12 &amp; ".html」の" &amp; A21 &amp; "htmlファイルです。"</f>
+        <v>３，修正対象のフォルダは、「母性」です。修正対象のhtmlは、「one.html」から「twentythree.html」の70htmlファイルです。</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="D22" t="str">
+        <f>"４，現在の" &amp; A12 &amp; ".html～" &amp; B12 &amp; " .htmlのファイル内に、one.htmlのような詳細な説明文は記載されていません。説明文を考えて追加していただきたいのですが可能でしょうか。可能であれば、簡潔に一文で説明文を追加していただきたいです。"</f>
+        <v>４，現在のone.html～twentythree .htmlのファイル内に、one.htmlのような詳細な説明文は記載されていません。説明文を考えて追加していただきたいのですが可能でしょうか。可能であれば、簡潔に一文で説明文を追加していただきたいです。</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="D23" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="D16" t="str">
-        <f>"・" &amp; A3 &amp; "フォルダ内「one.html」の【選択肢の解説】内で記載しているように、「選択肢番号、選択肢、→選択肢が正・誤の理由を一文で簡潔に」整えてください。"</f>
-        <v>・小児_事後課題フォルダ内「one.html」の【選択肢の解説】内で記載しているように、「選択肢番号、選択肢、→選択肢が正・誤の理由を一文で簡潔に」整えてください。</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="1">
-        <v>70</v>
-      </c>
-      <c r="D18" t="str">
-        <f>"３，修正対象のフォルダは、「" &amp; A3 &amp; "」です。修正対象のhtmlは、「" &amp; A9 &amp; ".html」から「" &amp; B9 &amp; ".html」の" &amp; A18 &amp; "htmlファイルです。"</f>
-        <v>３，修正対象のフォルダは、「小児_事後課題」です。修正対象のhtmlは、「one.html」から「seventy.html」の70htmlファイルです。</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="D20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="D21" t="str">
-        <f>"１，現在の" &amp; A9 &amp; ".html～" &amp; B9 &amp; " .htmlのファイル内に、one.htmlのような詳細な説明文は記載されていません。説明文を考えて追加していただきたいのですが可能でしょうか。可能であれば、簡潔に一文で説明文を追加していただきたいです。"</f>
-        <v>１，現在のone.html～seventy .htmlのファイル内に、one.htmlのような詳細な説明文は記載されていません。説明文を考えて追加していただきたいのですが可能でしょうか。可能であれば、簡潔に一文で説明文を追加していただきたいです。</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="D22" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -730,16 +734,16 @@
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!コピー作成">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
-                    <xdr:col>2</xdr:col>
-                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>381000</xdr:colOff>
                     <xdr:row>22</xdr:row>
-                    <xdr:rowOff>222250</xdr:rowOff>
+                    <xdr:rowOff>57150</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>6350</xdr:rowOff>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>571500</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>63500</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
